--- a/data/trans_orig/LAWTONBRODY_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY_2023-Provincia-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>6,01</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,75</t>
+          <t>5,84; 6,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,11</t>
+          <t>5,18; 6,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 6,28</t>
+          <t>5,61; 6,36</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>7,16</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,52</t>
+          <t>6,62; 7,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,15</t>
+          <t>5,29; 6,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,6</t>
+          <t>5,92; 6,59</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,12</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 6,74</t>
+          <t>5,73; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 6,32</t>
+          <t>5,45; 6,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 6,4</t>
+          <t>5,74; 6,39</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,63</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,2</t>
+          <t>6,41; 7,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 6,78</t>
+          <t>6,16; 6,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 6,86</t>
+          <t>6,4; 6,9</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,6</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,47</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,15</t>
+          <t>5,89; 7,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,81</t>
+          <t>5,92; 6,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 6,8</t>
+          <t>6,09; 6,79</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,54</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 6,66</t>
+          <t>5,76; 6,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,98</t>
+          <t>5,06; 5,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 6,16</t>
+          <t>5,51; 6,17</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,4</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,61</t>
+          <t>7,1; 7,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,83</t>
+          <t>6,04; 6,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,82</t>
+          <t>6,65; 7,08</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>7,04</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,7</t>
+          <t>7,32; 7,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,91</t>
+          <t>6,38; 6,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,22</t>
+          <t>6,86; 7,2</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,1</t>
+          <t>6,86; 7,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,35</t>
+          <t>6,08; 6,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,29</t>
+          <t>6,46; 6,65</t>
         </is>
       </c>
     </row>
